--- a/extraction_and_recoding_new/parameters/parameters_changed.xlsx
+++ b/extraction_and_recoding_new/parameters/parameters_changed.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="951">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=2020</t>
   </si>
   <si>
-    <t xml:space="preserve">loneliness</t>
+    <t xml:space="preserve">mh_loneliness</t>
   </si>
   <si>
     <t xml:space="preserve">Able to confide</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=2110</t>
   </si>
   <si>
-    <t xml:space="preserve">social_support_confide</t>
+    <t xml:space="preserve">mh_social_support_confide</t>
   </si>
   <si>
     <t xml:space="preserve">Had major operations</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=2415</t>
   </si>
   <si>
-    <t xml:space="preserve">hx_major_surgery_yn</t>
+    <t xml:space="preserve">sur_major_surgery</t>
   </si>
   <si>
     <t xml:space="preserve">Diabetes diagnosed by doctor</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=2443</t>
   </si>
   <si>
-    <t xml:space="preserve">dx_diabetes_doc_yn</t>
+    <t xml:space="preserve">dis_diabetes_doc_yn</t>
   </si>
   <si>
     <t xml:space="preserve">Cancer diagnosed by doctor</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=2453</t>
   </si>
   <si>
-    <t xml:space="preserve">dx_cancer_doc_yn</t>
+    <t xml:space="preserve">dis_cancer_doc_yn</t>
   </si>
   <si>
     <t xml:space="preserve">Age high blood pressure diagnosed</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=2966</t>
   </si>
   <si>
-    <t xml:space="preserve">age_dx_htn</t>
+    <t xml:space="preserve">dis_age_highbp</t>
   </si>
   <si>
     <t xml:space="preserve">Age high blood pressure diagnosed (years)</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=2976</t>
   </si>
   <si>
-    <t xml:space="preserve">age_dx_diabetes</t>
+    <t xml:space="preserve">dis_age_diabetes</t>
   </si>
   <si>
     <t xml:space="preserve">Age diabetes diagnosed (years)</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=3894</t>
   </si>
   <si>
-    <t xml:space="preserve">age_dx_mi</t>
+    <t xml:space="preserve">dis_age_mi</t>
   </si>
   <si>
     <t xml:space="preserve">Age heart attack diagnosed (years)</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=6150</t>
   </si>
   <si>
-    <t xml:space="preserve">dx_cvd_doc_yn</t>
+    <t xml:space="preserve">dis_cvd_doc_yn</t>
   </si>
   <si>
     <t xml:space="preserve">Medication for cholesterol, blood pressure, diabetes, or take exogenous hormones</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=20126</t>
   </si>
   <si>
-    <t xml:space="preserve">BPD_MD_status</t>
+    <t xml:space="preserve">mh_BPD_MD</t>
   </si>
   <si>
     <t xml:space="preserve">Neuroticism score</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=20127</t>
   </si>
   <si>
-    <t xml:space="preserve">Neuroticism_score</t>
+    <t xml:space="preserve">mh_neuroticism</t>
   </si>
   <si>
     <t xml:space="preserve">Pack years of smoking</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=22150</t>
   </si>
   <si>
-    <t xml:space="preserve">age_copd</t>
+    <t xml:space="preserve">dis_age_copd</t>
   </si>
   <si>
     <t xml:space="preserve">Age idiopathic pulmonary fibrosis diagnosed by doctor</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=22155</t>
   </si>
   <si>
-    <t xml:space="preserve">age_pulmonary_fibrosis</t>
+    <t xml:space="preserve">dis_age_pulmonary_fibrosis</t>
   </si>
   <si>
     <t xml:space="preserve">Average heart rate</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=23099</t>
   </si>
   <si>
-    <t xml:space="preserve">body_fat_pct </t>
+    <t xml:space="preserve">body_fat_pct</t>
   </si>
   <si>
     <t xml:space="preserve">Body fat percentage (percent)</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=40005</t>
   </si>
   <si>
-    <t xml:space="preserve">date_of_cancer</t>
+    <t xml:space="preserve">dis_date_of_cancer</t>
   </si>
   <si>
     <t xml:space="preserve">Histology of cancer tumour</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=40011</t>
   </si>
   <si>
-    <t xml:space="preserve">history_cancer_tumour</t>
+    <t xml:space="preserve">dis_history_cancer_tumour</t>
   </si>
   <si>
     <t xml:space="preserve">Saturated fat</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=100006</t>
   </si>
   <si>
-    <t xml:space="preserve">saturated _fat</t>
+    <t xml:space="preserve">saturated_fat</t>
   </si>
   <si>
     <t xml:space="preserve">Saturated fat (g)</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130200</t>
   </si>
   <si>
-    <t xml:space="preserve">chronic_hepatitis</t>
+    <t xml:space="preserve">dis_chronic_hepatitis</t>
   </si>
   <si>
     <t xml:space="preserve">Date E10 first reported (insulin-dependent diabetes mellitus)</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130706</t>
   </si>
   <si>
-    <t xml:space="preserve">dt_e10_first</t>
+    <t xml:space="preserve">dis_insulin_dep_diabetes</t>
   </si>
   <si>
     <t xml:space="preserve">Date E11 first reported (non-insulin-dependent diabetes mellitus)</t>
@@ -2564,19 +2564,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130708</t>
   </si>
   <si>
-    <t xml:space="preserve">dt_e11_first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date E12 first reported (malnutrition-related diabetes mellitus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date of the first occurrence of any code mapped to 3-character ICD10 E12. The code corresponds to \"malnutrition-related diabetes mellitus\". Note that events which were apparently before birth were omitted when constructing this data field.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dt_e12_first</t>
+    <t xml:space="preserve">dis_non_insulin_dep_diabetes</t>
   </si>
   <si>
     <t xml:space="preserve">Date F20 first reported (schizophrenia)</t>
@@ -2591,7 +2579,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130874</t>
   </si>
   <si>
-    <t xml:space="preserve">schizophrenia</t>
+    <t xml:space="preserve">dis_schizophrenia</t>
   </si>
   <si>
     <t xml:space="preserve">Date F32 first reported (depressive episode)</t>
@@ -2603,7 +2591,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130894</t>
   </si>
   <si>
-    <t xml:space="preserve">depr_single_icd</t>
+    <t xml:space="preserve">mh_depr_single_icd</t>
   </si>
   <si>
     <t xml:space="preserve">Date F33 first reported (recurrent depressive disorder)</t>
@@ -2615,7 +2603,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130896</t>
   </si>
   <si>
-    <t xml:space="preserve">depr_recurrent_icd</t>
+    <t xml:space="preserve">mh_depr_recurrent_icd</t>
   </si>
   <si>
     <t xml:space="preserve">Date F40 first reported (phobic anxiety disorders)</t>
@@ -2627,7 +2615,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130904</t>
   </si>
   <si>
-    <t xml:space="preserve">anxiety_phobic_icd</t>
+    <t xml:space="preserve">mh_anxiety_phobic_icd</t>
   </si>
   <si>
     <t xml:space="preserve">Date F41 first reported (other anxiety disorders)</t>
@@ -2639,7 +2627,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=130906</t>
   </si>
   <si>
-    <t xml:space="preserve">anxiety_general_icd</t>
+    <t xml:space="preserve">mh_anxiety_general_icd</t>
   </si>
   <si>
     <t xml:space="preserve">Date G20 first reported (parkinson's disease)</t>
@@ -2654,7 +2642,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131022</t>
   </si>
   <si>
-    <t xml:space="preserve">parkinsons_disease</t>
+    <t xml:space="preserve">dis_parkinsons_disease</t>
   </si>
   <si>
     <t xml:space="preserve">Date G30 first reported (alzheimer's disease)</t>
@@ -2666,7 +2654,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131036</t>
   </si>
   <si>
-    <t xml:space="preserve">alzheimers_disease</t>
+    <t xml:space="preserve">dis_alzheimers_disease</t>
   </si>
   <si>
     <t xml:space="preserve">Date G35 first reported (multiple sclerosis)</t>
@@ -2678,7 +2666,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131042</t>
   </si>
   <si>
-    <t xml:space="preserve">multiple_sclerosis</t>
+    <t xml:space="preserve">dis_multiple_sclerosis</t>
   </si>
   <si>
     <t xml:space="preserve">Date G43 first reported (migraine)</t>
@@ -2690,7 +2678,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131052</t>
   </si>
   <si>
-    <t xml:space="preserve">migraine</t>
+    <t xml:space="preserve">dis_migraine</t>
   </si>
   <si>
     <t xml:space="preserve">Date G44 first reported (other headache syndromes)</t>
@@ -2702,7 +2690,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131054</t>
   </si>
   <si>
-    <t xml:space="preserve">other_headaches</t>
+    <t xml:space="preserve">dis_other_headaches</t>
   </si>
   <si>
     <t xml:space="preserve">Date G47 first reported (sleep disorders)</t>
@@ -2714,7 +2702,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131060</t>
   </si>
   <si>
-    <t xml:space="preserve">sleep_disorders</t>
+    <t xml:space="preserve">dis_sleep_disorders</t>
   </si>
   <si>
     <t xml:space="preserve">Date I10 first reported (essential (primary) hypertension)</t>
@@ -2729,19 +2717,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131286</t>
   </si>
   <si>
-    <t xml:space="preserve">dt_l10_first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source of report of I10 (essential (primary) hypertension)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source of the first code mapped to 3-character ICD10 I10, and whether this code occurs in other source(s) with the same or a later event date. The code corresponds to \"essential (primary) hypertension\". See Resource 593 for details of how the first source was assigned.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src_l10_first</t>
+    <t xml:space="preserve">dis_dt_l10_first</t>
   </si>
   <si>
     <t xml:space="preserve">Date I12 first reported (hypertensive renal disease)</t>
@@ -2753,7 +2729,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131290</t>
   </si>
   <si>
-    <t xml:space="preserve">hypertensive_renal_disease</t>
+    <t xml:space="preserve">dis_hypertensive_renal_disease</t>
   </si>
   <si>
     <t xml:space="preserve">Date I13 first reported (hypertensive heart and renal disease)</t>
@@ -2765,7 +2741,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131292</t>
   </si>
   <si>
-    <t xml:space="preserve">hypertensive_heart_renal_disease</t>
+    <t xml:space="preserve">dis_hypertensive_heart_renal_disease</t>
   </si>
   <si>
     <t xml:space="preserve">Date J45 first reported (asthma)</t>
@@ -2780,7 +2756,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131494</t>
   </si>
   <si>
-    <t xml:space="preserve">asthma</t>
+    <t xml:space="preserve">dis_asthma</t>
   </si>
   <si>
     <t xml:space="preserve">Date K50 first reported (crohn's disease [regional enteritis])</t>
@@ -2795,7 +2771,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131626</t>
   </si>
   <si>
-    <t xml:space="preserve">crohns_disease</t>
+    <t xml:space="preserve">dis_crohns_disease</t>
   </si>
   <si>
     <t xml:space="preserve">Date K51 first reported (ulcerative colitis)</t>
@@ -2807,7 +2783,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131628</t>
   </si>
   <si>
-    <t xml:space="preserve">ulcerative_colitis</t>
+    <t xml:space="preserve">dis_ulcerative_colitis</t>
   </si>
   <si>
     <t xml:space="preserve">Date K70 first reported (alcoholic liver disease)</t>
@@ -2819,7 +2795,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131658</t>
   </si>
   <si>
-    <t xml:space="preserve">alcoholic _liver_disease</t>
+    <t xml:space="preserve">dis_alcoholic_liver_disease</t>
   </si>
   <si>
     <t xml:space="preserve">Date K74 first reported (fibrosis and cirrhosis of liver)</t>
@@ -2831,7 +2807,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131666</t>
   </si>
   <si>
-    <t xml:space="preserve">liver_fibrosis_and_cirrhosis</t>
+    <t xml:space="preserve">dis_liver_fibrosis_and_cirrhosis</t>
   </si>
   <si>
     <t xml:space="preserve">Date L40 first reported (psoriasis)</t>
@@ -2846,7 +2822,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131742</t>
   </si>
   <si>
-    <t xml:space="preserve">psoriasis</t>
+    <t xml:space="preserve">dis_psoriasis</t>
   </si>
   <si>
     <t xml:space="preserve">Date L93 first reported (lupus erythematosus)</t>
@@ -2858,7 +2834,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131828</t>
   </si>
   <si>
-    <t xml:space="preserve">lupus</t>
+    <t xml:space="preserve">dis_lupus</t>
   </si>
   <si>
     <t xml:space="preserve">Date M05 first reported (seropositive rheumatoid arthritis)</t>
@@ -2873,7 +2849,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=131848</t>
   </si>
   <si>
-    <t xml:space="preserve">rheumatoid_arthritis</t>
+    <t xml:space="preserve">dis_rheumatoid_arthritis</t>
   </si>
   <si>
     <t xml:space="preserve">Date N18 first reported (chronic renal failure)</t>
@@ -2888,7 +2864,7 @@
     <t xml:space="preserve">http://biobank.ndph.ox.ac.uk/ukb/field.cgi?id=132032</t>
   </si>
   <si>
-    <t xml:space="preserve">chronic_renal_failure</t>
+    <t xml:space="preserve">dis_chronic_renal_failure</t>
   </si>
 </sst>
 </file>
@@ -11247,7 +11223,7 @@
         <v>851</v>
       </c>
       <c r="B160" t="n">
-        <v>8</v>
+        <v>1461</v>
       </c>
       <c r="C160" t="s">
         <v>852</v>
@@ -11257,13 +11233,13 @@
         <v>19</v>
       </c>
       <c r="F160" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="G160" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H160" t="n">
-        <v>130710</v>
+        <v>130874</v>
       </c>
       <c r="I160" t="s">
         <v>27</v>
@@ -11272,7 +11248,7 @@
         <v>819</v>
       </c>
       <c r="K160" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="L160" t="s">
         <v>851</v>
@@ -11293,26 +11269,26 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B161" t="n">
-        <v>1461</v>
+        <v>63043</v>
       </c>
       <c r="C161" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D161"/>
       <c r="E161" t="s">
         <v>19</v>
       </c>
       <c r="F161" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G161" t="s">
         <v>858</v>
       </c>
       <c r="H161" t="n">
-        <v>130874</v>
+        <v>130894</v>
       </c>
       <c r="I161" t="s">
         <v>27</v>
@@ -11324,14 +11300,14 @@
         <v>859</v>
       </c>
       <c r="L161" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="M161"/>
       <c r="N161" t="s">
         <v>19</v>
       </c>
       <c r="O161" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="P161" t="s">
         <v>19</v>
@@ -11345,7 +11321,7 @@
         <v>860</v>
       </c>
       <c r="B162" t="n">
-        <v>63043</v>
+        <v>3966</v>
       </c>
       <c r="C162" t="s">
         <v>861</v>
@@ -11355,13 +11331,13 @@
         <v>19</v>
       </c>
       <c r="F162" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G162" t="s">
         <v>862</v>
       </c>
       <c r="H162" t="n">
-        <v>130894</v>
+        <v>130896</v>
       </c>
       <c r="I162" t="s">
         <v>27</v>
@@ -11394,7 +11370,7 @@
         <v>864</v>
       </c>
       <c r="B163" t="n">
-        <v>3966</v>
+        <v>4499</v>
       </c>
       <c r="C163" t="s">
         <v>865</v>
@@ -11404,13 +11380,13 @@
         <v>19</v>
       </c>
       <c r="F163" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G163" t="s">
         <v>866</v>
       </c>
       <c r="H163" t="n">
-        <v>130896</v>
+        <v>130904</v>
       </c>
       <c r="I163" t="s">
         <v>27</v>
@@ -11443,7 +11419,7 @@
         <v>868</v>
       </c>
       <c r="B164" t="n">
-        <v>4499</v>
+        <v>42018</v>
       </c>
       <c r="C164" t="s">
         <v>869</v>
@@ -11453,13 +11429,13 @@
         <v>19</v>
       </c>
       <c r="F164" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G164" t="s">
         <v>870</v>
       </c>
       <c r="H164" t="n">
-        <v>130904</v>
+        <v>130906</v>
       </c>
       <c r="I164" t="s">
         <v>27</v>
@@ -11492,7 +11468,7 @@
         <v>872</v>
       </c>
       <c r="B165" t="n">
-        <v>42018</v>
+        <v>4564</v>
       </c>
       <c r="C165" t="s">
         <v>873</v>
@@ -11502,13 +11478,13 @@
         <v>19</v>
       </c>
       <c r="F165" t="s">
-        <v>857</v>
+        <v>874</v>
       </c>
       <c r="G165" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H165" t="n">
-        <v>130906</v>
+        <v>131022</v>
       </c>
       <c r="I165" t="s">
         <v>27</v>
@@ -11517,7 +11493,7 @@
         <v>819</v>
       </c>
       <c r="K165" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="L165" t="s">
         <v>872</v>
@@ -11538,26 +11514,26 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B166" t="n">
-        <v>4564</v>
+        <v>4473</v>
       </c>
       <c r="C166" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D166"/>
       <c r="E166" t="s">
         <v>19</v>
       </c>
       <c r="F166" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="G166" t="s">
         <v>879</v>
       </c>
       <c r="H166" t="n">
-        <v>131022</v>
+        <v>131036</v>
       </c>
       <c r="I166" t="s">
         <v>27</v>
@@ -11569,14 +11545,14 @@
         <v>880</v>
       </c>
       <c r="L166" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M166"/>
       <c r="N166" t="s">
         <v>19</v>
       </c>
       <c r="O166" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="P166" t="s">
         <v>19</v>
@@ -11590,7 +11566,7 @@
         <v>881</v>
       </c>
       <c r="B167" t="n">
-        <v>4473</v>
+        <v>2595</v>
       </c>
       <c r="C167" t="s">
         <v>882</v>
@@ -11600,13 +11576,13 @@
         <v>19</v>
       </c>
       <c r="F167" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="G167" t="s">
         <v>883</v>
       </c>
       <c r="H167" t="n">
-        <v>131036</v>
+        <v>131042</v>
       </c>
       <c r="I167" t="s">
         <v>27</v>
@@ -11639,7 +11615,7 @@
         <v>885</v>
       </c>
       <c r="B168" t="n">
-        <v>2595</v>
+        <v>27402</v>
       </c>
       <c r="C168" t="s">
         <v>886</v>
@@ -11649,13 +11625,13 @@
         <v>19</v>
       </c>
       <c r="F168" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="G168" t="s">
         <v>887</v>
       </c>
       <c r="H168" t="n">
-        <v>131042</v>
+        <v>131052</v>
       </c>
       <c r="I168" t="s">
         <v>27</v>
@@ -11688,7 +11664,7 @@
         <v>889</v>
       </c>
       <c r="B169" t="n">
-        <v>27402</v>
+        <v>6180</v>
       </c>
       <c r="C169" t="s">
         <v>890</v>
@@ -11698,13 +11674,13 @@
         <v>19</v>
       </c>
       <c r="F169" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="G169" t="s">
         <v>891</v>
       </c>
       <c r="H169" t="n">
-        <v>131052</v>
+        <v>131054</v>
       </c>
       <c r="I169" t="s">
         <v>27</v>
@@ -11737,7 +11713,7 @@
         <v>893</v>
       </c>
       <c r="B170" t="n">
-        <v>6180</v>
+        <v>21013</v>
       </c>
       <c r="C170" t="s">
         <v>894</v>
@@ -11747,13 +11723,13 @@
         <v>19</v>
       </c>
       <c r="F170" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="G170" t="s">
         <v>895</v>
       </c>
       <c r="H170" t="n">
-        <v>131054</v>
+        <v>131060</v>
       </c>
       <c r="I170" t="s">
         <v>27</v>
@@ -11786,7 +11762,7 @@
         <v>897</v>
       </c>
       <c r="B171" t="n">
-        <v>21013</v>
+        <v>203053</v>
       </c>
       <c r="C171" t="s">
         <v>898</v>
@@ -11796,13 +11772,13 @@
         <v>19</v>
       </c>
       <c r="F171" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="G171" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H171" t="n">
-        <v>131060</v>
+        <v>131286</v>
       </c>
       <c r="I171" t="s">
         <v>27</v>
@@ -11811,7 +11787,7 @@
         <v>819</v>
       </c>
       <c r="K171" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="L171" t="s">
         <v>897</v>
@@ -11832,26 +11808,26 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B172" t="n">
-        <v>203053</v>
+        <v>2283</v>
       </c>
       <c r="C172" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D172"/>
       <c r="E172" t="s">
         <v>19</v>
       </c>
       <c r="F172" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="G172" t="s">
         <v>904</v>
       </c>
       <c r="H172" t="n">
-        <v>131286</v>
+        <v>131290</v>
       </c>
       <c r="I172" t="s">
         <v>27</v>
@@ -11863,14 +11839,14 @@
         <v>905</v>
       </c>
       <c r="L172" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M172"/>
       <c r="N172" t="s">
         <v>19</v>
       </c>
       <c r="O172" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="P172" t="s">
         <v>19</v>
@@ -11884,7 +11860,7 @@
         <v>906</v>
       </c>
       <c r="B173" t="n">
-        <v>203053</v>
+        <v>199</v>
       </c>
       <c r="C173" t="s">
         <v>907</v>
@@ -11894,19 +11870,19 @@
         <v>19</v>
       </c>
       <c r="F173" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="G173" t="s">
         <v>908</v>
       </c>
       <c r="H173" t="n">
-        <v>131287</v>
+        <v>131292</v>
       </c>
       <c r="I173" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J173" t="n">
-        <v>2171</v>
+        <v>819</v>
       </c>
       <c r="K173" t="s">
         <v>909</v>
@@ -11933,7 +11909,7 @@
         <v>910</v>
       </c>
       <c r="B174" t="n">
-        <v>2283</v>
+        <v>74348</v>
       </c>
       <c r="C174" t="s">
         <v>911</v>
@@ -11943,13 +11919,13 @@
         <v>19</v>
       </c>
       <c r="F174" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="G174" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H174" t="n">
-        <v>131290</v>
+        <v>131494</v>
       </c>
       <c r="I174" t="s">
         <v>27</v>
@@ -11958,7 +11934,7 @@
         <v>819</v>
       </c>
       <c r="K174" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="L174" t="s">
         <v>910</v>
@@ -11979,26 +11955,26 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B175" t="n">
-        <v>199</v>
+        <v>3502</v>
       </c>
       <c r="C175" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D175"/>
       <c r="E175" t="s">
         <v>19</v>
       </c>
       <c r="F175" t="s">
-        <v>903</v>
+        <v>917</v>
       </c>
       <c r="G175" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="H175" t="n">
-        <v>131292</v>
+        <v>131626</v>
       </c>
       <c r="I175" t="s">
         <v>27</v>
@@ -12007,17 +11983,17 @@
         <v>819</v>
       </c>
       <c r="K175" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="L175" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M175"/>
       <c r="N175" t="s">
         <v>19</v>
       </c>
       <c r="O175" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="P175" t="s">
         <v>19</v>
@@ -12028,26 +12004,26 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B176" t="n">
-        <v>74348</v>
+        <v>6698</v>
       </c>
       <c r="C176" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D176"/>
       <c r="E176" t="s">
         <v>19</v>
       </c>
       <c r="F176" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="G176" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H176" t="n">
-        <v>131494</v>
+        <v>131628</v>
       </c>
       <c r="I176" t="s">
         <v>27</v>
@@ -12056,17 +12032,17 @@
         <v>819</v>
       </c>
       <c r="K176" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L176" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="M176"/>
       <c r="N176" t="s">
         <v>19</v>
       </c>
       <c r="O176" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="P176" t="s">
         <v>19</v>
@@ -12077,26 +12053,26 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B177" t="n">
-        <v>3502</v>
+        <v>2441</v>
       </c>
       <c r="C177" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D177"/>
       <c r="E177" t="s">
         <v>19</v>
       </c>
       <c r="F177" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G177" t="s">
         <v>926</v>
       </c>
       <c r="H177" t="n">
-        <v>131626</v>
+        <v>131658</v>
       </c>
       <c r="I177" t="s">
         <v>27</v>
@@ -12108,14 +12084,14 @@
         <v>927</v>
       </c>
       <c r="L177" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="M177"/>
       <c r="N177" t="s">
         <v>19</v>
       </c>
       <c r="O177" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="P177" t="s">
         <v>19</v>
@@ -12129,7 +12105,7 @@
         <v>928</v>
       </c>
       <c r="B178" t="n">
-        <v>6698</v>
+        <v>3104</v>
       </c>
       <c r="C178" t="s">
         <v>929</v>
@@ -12139,13 +12115,13 @@
         <v>19</v>
       </c>
       <c r="F178" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="G178" t="s">
         <v>930</v>
       </c>
       <c r="H178" t="n">
-        <v>131628</v>
+        <v>131666</v>
       </c>
       <c r="I178" t="s">
         <v>27</v>
@@ -12178,7 +12154,7 @@
         <v>932</v>
       </c>
       <c r="B179" t="n">
-        <v>2441</v>
+        <v>15928</v>
       </c>
       <c r="C179" t="s">
         <v>933</v>
@@ -12188,13 +12164,13 @@
         <v>19</v>
       </c>
       <c r="F179" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="G179" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H179" t="n">
-        <v>131658</v>
+        <v>131742</v>
       </c>
       <c r="I179" t="s">
         <v>27</v>
@@ -12203,7 +12179,7 @@
         <v>819</v>
       </c>
       <c r="K179" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="L179" t="s">
         <v>932</v>
@@ -12224,26 +12200,26 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B180" t="n">
-        <v>3104</v>
+        <v>552</v>
       </c>
       <c r="C180" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D180"/>
       <c r="E180" t="s">
         <v>19</v>
       </c>
       <c r="F180" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="G180" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H180" t="n">
-        <v>131666</v>
+        <v>131828</v>
       </c>
       <c r="I180" t="s">
         <v>27</v>
@@ -12252,17 +12228,17 @@
         <v>819</v>
       </c>
       <c r="K180" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L180" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M180"/>
       <c r="N180" t="s">
         <v>19</v>
       </c>
       <c r="O180" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="P180" t="s">
         <v>19</v>
@@ -12273,26 +12249,26 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B181" t="n">
-        <v>15928</v>
+        <v>1534</v>
       </c>
       <c r="C181" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D181"/>
       <c r="E181" t="s">
         <v>19</v>
       </c>
       <c r="F181" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="G181" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H181" t="n">
-        <v>131742</v>
+        <v>131848</v>
       </c>
       <c r="I181" t="s">
         <v>27</v>
@@ -12301,17 +12277,17 @@
         <v>819</v>
       </c>
       <c r="K181" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="L181" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="M181"/>
       <c r="N181" t="s">
         <v>19</v>
       </c>
       <c r="O181" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="P181" t="s">
         <v>19</v>
@@ -12322,26 +12298,26 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B182" t="n">
-        <v>552</v>
+        <v>31231</v>
       </c>
       <c r="C182" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D182"/>
       <c r="E182" t="s">
         <v>19</v>
       </c>
       <c r="F182" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="G182" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="H182" t="n">
-        <v>131828</v>
+        <v>132032</v>
       </c>
       <c r="I182" t="s">
         <v>27</v>
@@ -12350,120 +12326,22 @@
         <v>819</v>
       </c>
       <c r="K182" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="L182" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="M182"/>
       <c r="N182" t="s">
         <v>19</v>
       </c>
       <c r="O182" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="P182" t="s">
         <v>19</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>949</v>
-      </c>
-      <c r="B183" t="n">
-        <v>1534</v>
-      </c>
-      <c r="C183" t="s">
-        <v>950</v>
-      </c>
-      <c r="D183"/>
-      <c r="E183" t="s">
-        <v>19</v>
-      </c>
-      <c r="F183" t="s">
-        <v>951</v>
-      </c>
-      <c r="G183" t="s">
-        <v>952</v>
-      </c>
-      <c r="H183" t="n">
-        <v>131848</v>
-      </c>
-      <c r="I183" t="s">
-        <v>27</v>
-      </c>
-      <c r="J183" t="n">
-        <v>819</v>
-      </c>
-      <c r="K183" t="s">
-        <v>953</v>
-      </c>
-      <c r="L183" t="s">
-        <v>949</v>
-      </c>
-      <c r="M183"/>
-      <c r="N183" t="s">
-        <v>19</v>
-      </c>
-      <c r="O183" t="s">
-        <v>949</v>
-      </c>
-      <c r="P183" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>954</v>
-      </c>
-      <c r="B184" t="n">
-        <v>31231</v>
-      </c>
-      <c r="C184" t="s">
-        <v>955</v>
-      </c>
-      <c r="D184"/>
-      <c r="E184" t="s">
-        <v>19</v>
-      </c>
-      <c r="F184" t="s">
-        <v>956</v>
-      </c>
-      <c r="G184" t="s">
-        <v>957</v>
-      </c>
-      <c r="H184" t="n">
-        <v>132032</v>
-      </c>
-      <c r="I184" t="s">
-        <v>27</v>
-      </c>
-      <c r="J184" t="n">
-        <v>819</v>
-      </c>
-      <c r="K184" t="s">
-        <v>958</v>
-      </c>
-      <c r="L184" t="s">
-        <v>954</v>
-      </c>
-      <c r="M184"/>
-      <c r="N184" t="s">
-        <v>19</v>
-      </c>
-      <c r="O184" t="s">
-        <v>954</v>
-      </c>
-      <c r="P184" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q184" t="n">
         <v>0</v>
       </c>
     </row>

--- a/extraction_and_recoding_new/parameters/parameters_changed.xlsx
+++ b/extraction_and_recoding_new/parameters/parameters_changed.xlsx
@@ -101,6 +101,9 @@
     <t xml:space="preserve">dob</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve">Waist circumference</t>
   </si>
   <si>
@@ -1254,9 +1257,6 @@
   </si>
   <si>
     <t xml:space="preserve">Average heart rate (bpm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">Body fat percentage</t>
@@ -3336,7 +3336,7 @@
         <v>24</v>
       </c>
       <c r="P3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -3344,47 +3344,47 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>500290</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
         <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4"/>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N4" t="s">
         <v>19</v>
       </c>
       <c r="O4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P4" t="s">
         <v>19</v>
@@ -3395,47 +3395,47 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" t="n">
         <v>500226</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
         <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5"/>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5" t="s">
         <v>19</v>
       </c>
       <c r="O5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P5" t="s">
         <v>19</v>
@@ -3446,23 +3446,23 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>502366</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6"/>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H6" t="n">
         <v>53</v>
@@ -3472,17 +3472,17 @@
       </c>
       <c r="J6"/>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M6"/>
       <c r="N6" t="s">
         <v>19</v>
       </c>
       <c r="O6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P6" t="s">
         <v>19</v>
@@ -3493,50 +3493,50 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" t="n">
         <v>51604</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" t="n">
         <v>93</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7"/>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
         <v>19</v>
       </c>
       <c r="O7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3544,50 +3544,50 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" t="n">
         <v>51604</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H8" t="n">
         <v>94</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J8"/>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P8" t="s">
         <v>56</v>
-      </c>
-      <c r="M8" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P8" t="s">
-        <v>55</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -3595,43 +3595,43 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" t="n">
         <v>501525</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9"/>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" t="n">
         <v>137</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J9"/>
       <c r="K9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M9"/>
       <c r="N9" t="s">
         <v>19</v>
       </c>
       <c r="O9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P9" t="s">
         <v>19</v>
@@ -3642,23 +3642,23 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" t="n">
         <v>497480</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H10" t="n">
         <v>738</v>
@@ -3670,17 +3670,17 @@
         <v>100294</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M10"/>
       <c r="N10" t="s">
         <v>19</v>
       </c>
       <c r="O10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P10" t="s">
         <v>19</v>
@@ -3691,23 +3691,23 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" t="n">
         <v>288702</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11"/>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H11" t="n">
         <v>806</v>
@@ -3719,17 +3719,17 @@
         <v>100301</v>
       </c>
       <c r="K11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M11"/>
       <c r="N11" t="s">
         <v>19</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
         <v>19</v>
@@ -3740,49 +3740,49 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" t="n">
         <v>337333</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" t="n">
         <v>845</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J12" t="n">
         <v>100306</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N12" t="s">
         <v>19</v>
       </c>
       <c r="O12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P12" t="s">
         <v>19</v>
@@ -3793,49 +3793,49 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" t="n">
         <v>501507</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13" t="n">
         <v>1070</v>
       </c>
       <c r="I13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J13" t="n">
         <v>100329</v>
       </c>
       <c r="K13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N13" t="s">
         <v>19</v>
       </c>
       <c r="O13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P13" t="s">
         <v>19</v>
@@ -3846,49 +3846,49 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B14" t="n">
         <v>498824</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" t="n">
         <v>1080</v>
       </c>
       <c r="I14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J14" t="n">
         <v>100329</v>
       </c>
       <c r="K14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N14" t="s">
         <v>19</v>
       </c>
       <c r="O14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P14" t="s">
         <v>19</v>
@@ -3899,49 +3899,49 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B15" t="n">
         <v>501295</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H15" t="n">
         <v>1090</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J15" t="n">
         <v>100329</v>
       </c>
       <c r="K15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N15" t="s">
         <v>19</v>
       </c>
       <c r="O15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P15" t="s">
         <v>19</v>
@@ -3952,23 +3952,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B16" t="n">
         <v>501295</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D16"/>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H16" t="n">
         <v>1100</v>
@@ -3980,17 +3980,17 @@
         <v>100334</v>
       </c>
       <c r="K16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M16"/>
       <c r="N16" t="s">
         <v>19</v>
       </c>
       <c r="O16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P16" t="s">
         <v>19</v>
@@ -4001,49 +4001,49 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B17" t="n">
         <v>501504</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H17" t="n">
         <v>1160</v>
       </c>
       <c r="I17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J17" t="n">
         <v>100291</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N17" t="s">
         <v>19</v>
       </c>
       <c r="O17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P17" t="s">
         <v>19</v>
@@ -4054,23 +4054,23 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B18" t="n">
         <v>501500</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D18"/>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H18" t="n">
         <v>1200</v>
@@ -4082,17 +4082,17 @@
         <v>100343</v>
       </c>
       <c r="K18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M18"/>
       <c r="N18" t="s">
         <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P18" t="s">
         <v>19</v>
@@ -4103,23 +4103,23 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B19" t="n">
         <v>501500</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D19"/>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H19" t="n">
         <v>1239</v>
@@ -4131,17 +4131,17 @@
         <v>100347</v>
       </c>
       <c r="K19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M19"/>
       <c r="N19" t="s">
         <v>19</v>
       </c>
       <c r="O19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P19" t="s">
         <v>19</v>
@@ -4152,23 +4152,23 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B20" t="n">
         <v>464200</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D20"/>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H20" t="n">
         <v>1249</v>
@@ -4180,17 +4180,17 @@
         <v>100348</v>
       </c>
       <c r="K20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M20"/>
       <c r="N20" t="s">
         <v>19</v>
       </c>
       <c r="O20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P20" t="s">
         <v>19</v>
@@ -4201,49 +4201,49 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B21" t="n">
         <v>501498</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H21" t="n">
         <v>1289</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J21" t="n">
         <v>100373</v>
       </c>
       <c r="K21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N21" t="s">
         <v>19</v>
       </c>
       <c r="O21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P21" t="s">
         <v>19</v>
@@ -4254,49 +4254,49 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B22" t="n">
         <v>501498</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H22" t="n">
         <v>1299</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J22" t="n">
         <v>100373</v>
       </c>
       <c r="K22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N22" t="s">
         <v>19</v>
       </c>
       <c r="O22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P22" t="s">
         <v>19</v>
@@ -4307,49 +4307,49 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B23" t="n">
         <v>501498</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H23" t="n">
         <v>1309</v>
       </c>
       <c r="I23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J23" t="n">
         <v>100373</v>
       </c>
       <c r="K23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N23" t="s">
         <v>19</v>
       </c>
       <c r="O23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P23" t="s">
         <v>19</v>
@@ -4360,49 +4360,49 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B24" t="n">
         <v>501497</v>
       </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H24" t="n">
         <v>1319</v>
       </c>
       <c r="I24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J24" t="n">
         <v>100373</v>
       </c>
       <c r="K24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N24" t="s">
         <v>19</v>
       </c>
       <c r="O24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P24" t="s">
         <v>19</v>
@@ -4413,23 +4413,23 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B25" t="n">
         <v>501497</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D25"/>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H25" t="n">
         <v>1329</v>
@@ -4441,17 +4441,17 @@
         <v>100377</v>
       </c>
       <c r="K25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M25"/>
       <c r="N25" t="s">
         <v>19</v>
       </c>
       <c r="O25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P25" t="s">
         <v>19</v>
@@ -4462,23 +4462,23 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B26" t="n">
         <v>501497</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D26"/>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H26" t="n">
         <v>1339</v>
@@ -4490,17 +4490,17 @@
         <v>100377</v>
       </c>
       <c r="K26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M26"/>
       <c r="N26" t="s">
         <v>19</v>
       </c>
       <c r="O26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P26" t="s">
         <v>19</v>
@@ -4511,23 +4511,23 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B27" t="n">
         <v>501496</v>
       </c>
       <c r="C27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D27"/>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H27" t="n">
         <v>1349</v>
@@ -4539,17 +4539,17 @@
         <v>100377</v>
       </c>
       <c r="K27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M27"/>
       <c r="N27" t="s">
         <v>19</v>
       </c>
       <c r="O27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P27" t="s">
         <v>19</v>
@@ -4560,23 +4560,23 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B28" t="n">
         <v>501496</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D28"/>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H28" t="n">
         <v>1369</v>
@@ -4588,17 +4588,17 @@
         <v>100377</v>
       </c>
       <c r="K28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M28"/>
       <c r="N28" t="s">
         <v>19</v>
       </c>
       <c r="O28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P28" t="s">
         <v>19</v>
@@ -4609,23 +4609,23 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B29" t="n">
         <v>501496</v>
       </c>
       <c r="C29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D29"/>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H29" t="n">
         <v>1379</v>
@@ -4637,17 +4637,17 @@
         <v>100377</v>
       </c>
       <c r="K29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M29"/>
       <c r="N29" t="s">
         <v>19</v>
       </c>
       <c r="O29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P29" t="s">
         <v>19</v>
@@ -4658,23 +4658,23 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B30" t="n">
         <v>501494</v>
       </c>
       <c r="C30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D30"/>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H30" t="n">
         <v>1389</v>
@@ -4686,17 +4686,17 @@
         <v>100377</v>
       </c>
       <c r="K30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M30"/>
       <c r="N30" t="s">
         <v>19</v>
       </c>
       <c r="O30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P30" t="s">
         <v>19</v>
@@ -4707,23 +4707,23 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B31" t="n">
         <v>490408</v>
       </c>
       <c r="C31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D31"/>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G31" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H31" t="n">
         <v>1408</v>
@@ -4735,17 +4735,17 @@
         <v>100377</v>
       </c>
       <c r="K31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M31"/>
       <c r="N31" t="s">
         <v>19</v>
       </c>
       <c r="O31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P31" t="s">
         <v>19</v>
@@ -4756,23 +4756,23 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B32" t="n">
         <v>501432</v>
       </c>
       <c r="C32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D32"/>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H32" t="n">
         <v>1418</v>
@@ -4784,17 +4784,17 @@
         <v>100387</v>
       </c>
       <c r="K32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M32"/>
       <c r="N32" t="s">
         <v>19</v>
       </c>
       <c r="O32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P32" t="s">
         <v>19</v>
@@ -4805,49 +4805,49 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="n">
         <v>498812</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H33" t="n">
         <v>1438</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J33" t="n">
         <v>100373</v>
       </c>
       <c r="K33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" t="s">
         <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P33" t="s">
         <v>19</v>
@@ -4858,23 +4858,23 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B34" t="n">
         <v>484235</v>
       </c>
       <c r="C34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D34"/>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H34" t="n">
         <v>1448</v>
@@ -4886,17 +4886,17 @@
         <v>100391</v>
       </c>
       <c r="K34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M34"/>
       <c r="N34" t="s">
         <v>19</v>
       </c>
       <c r="O34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P34" t="s">
         <v>19</v>
@@ -4907,49 +4907,49 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B35" t="n">
         <v>501400</v>
       </c>
       <c r="C35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H35" t="n">
         <v>1458</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J35" t="n">
         <v>100373</v>
       </c>
       <c r="K35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N35" t="s">
         <v>19</v>
       </c>
       <c r="O35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P35" t="s">
         <v>19</v>
@@ -4960,23 +4960,23 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B36" t="n">
         <v>420594</v>
       </c>
       <c r="C36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D36"/>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H36" t="n">
         <v>1468</v>
@@ -4988,17 +4988,17 @@
         <v>100393</v>
       </c>
       <c r="K36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M36"/>
       <c r="N36" t="s">
         <v>19</v>
       </c>
       <c r="O36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P36" t="s">
         <v>19</v>
@@ -5009,23 +5009,23 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B37" t="n">
         <v>501494</v>
       </c>
       <c r="C37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D37"/>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H37" t="n">
         <v>1478</v>
@@ -5037,17 +5037,17 @@
         <v>100394</v>
       </c>
       <c r="K37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M37"/>
       <c r="N37" t="s">
         <v>19</v>
       </c>
       <c r="O37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P37" t="s">
         <v>19</v>
@@ -5058,49 +5058,49 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B38" t="n">
         <v>501494</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H38" t="n">
         <v>1488</v>
       </c>
       <c r="I38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J38" t="n">
         <v>100373</v>
       </c>
       <c r="K38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N38" t="s">
         <v>19</v>
       </c>
       <c r="O38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P38" t="s">
         <v>19</v>
@@ -5111,52 +5111,52 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B39" t="n">
         <v>501494</v>
       </c>
       <c r="C39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H39" t="n">
         <v>1498</v>
       </c>
       <c r="I39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J39" t="n">
         <v>100373</v>
       </c>
       <c r="K39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N39" t="s">
         <v>19</v>
       </c>
       <c r="O39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P39" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -5164,49 +5164,49 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B40" t="n">
         <v>501494</v>
       </c>
       <c r="C40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H40" t="n">
         <v>1528</v>
       </c>
       <c r="I40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J40" t="n">
         <v>100373</v>
       </c>
       <c r="K40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N40" t="s">
         <v>19</v>
       </c>
       <c r="O40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P40" t="s">
         <v>19</v>
@@ -5217,23 +5217,23 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B41" t="n">
         <v>501494</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D41"/>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H41" t="n">
         <v>1558</v>
@@ -5245,17 +5245,17 @@
         <v>100402</v>
       </c>
       <c r="K41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L41" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M41"/>
       <c r="N41" t="s">
         <v>19</v>
       </c>
       <c r="O41" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P41" t="s">
         <v>19</v>
@@ -5266,23 +5266,23 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B42" t="n">
         <v>501484</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D42"/>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H42" t="n">
         <v>2020</v>
@@ -5294,17 +5294,17 @@
         <v>100349</v>
       </c>
       <c r="K42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M42"/>
       <c r="N42" t="s">
         <v>19</v>
       </c>
       <c r="O42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P42" t="s">
         <v>19</v>
@@ -5315,23 +5315,23 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B43" t="n">
         <v>501479</v>
       </c>
       <c r="C43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D43"/>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F43" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H43" t="n">
         <v>2110</v>
@@ -5343,17 +5343,17 @@
         <v>100501</v>
       </c>
       <c r="K43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M43"/>
       <c r="N43" t="s">
         <v>19</v>
       </c>
       <c r="O43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P43" t="s">
         <v>19</v>
@@ -5364,23 +5364,23 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B44" t="n">
         <v>228611</v>
       </c>
       <c r="C44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D44"/>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F44" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H44" t="n">
         <v>2415</v>
@@ -5392,17 +5392,17 @@
         <v>100603</v>
       </c>
       <c r="K44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M44"/>
       <c r="N44" t="s">
         <v>19</v>
       </c>
       <c r="O44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P44" t="s">
         <v>19</v>
@@ -5413,23 +5413,23 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B45" t="n">
         <v>501460</v>
       </c>
       <c r="C45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D45"/>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H45" t="n">
         <v>2443</v>
@@ -5441,17 +5441,17 @@
         <v>100349</v>
       </c>
       <c r="K45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M45"/>
       <c r="N45" t="s">
         <v>19</v>
       </c>
       <c r="O45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P45" t="s">
         <v>19</v>
@@ -5462,23 +5462,23 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B46" t="n">
         <v>501460</v>
       </c>
       <c r="C46" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D46"/>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H46" t="n">
         <v>2453</v>
@@ -5490,17 +5490,17 @@
         <v>100603</v>
       </c>
       <c r="K46" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M46"/>
       <c r="N46" t="s">
         <v>19</v>
       </c>
       <c r="O46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P46" t="s">
         <v>19</v>
@@ -5511,49 +5511,49 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B47" t="n">
         <v>143703</v>
       </c>
       <c r="C47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G47" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H47" t="n">
         <v>2966</v>
       </c>
       <c r="I47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J47" t="n">
         <v>100291</v>
       </c>
       <c r="K47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L47" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N47" t="s">
         <v>19</v>
       </c>
       <c r="O47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P47" t="s">
         <v>19</v>
@@ -5564,49 +5564,49 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B48" t="n">
         <v>27887</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H48" t="n">
         <v>2976</v>
       </c>
       <c r="I48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J48" t="n">
         <v>100291</v>
       </c>
       <c r="K48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M48" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N48" t="s">
         <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P48" t="s">
         <v>19</v>
@@ -5617,50 +5617,50 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B49" t="n">
         <v>457396</v>
       </c>
       <c r="C49" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D49" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F49" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G49" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H49" t="n">
         <v>3062</v>
       </c>
       <c r="I49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J49"/>
       <c r="K49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M49" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N49" t="s">
         <v>19</v>
       </c>
       <c r="O49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -5668,50 +5668,50 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B50" t="n">
         <v>457396</v>
       </c>
       <c r="C50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H50" t="n">
         <v>3063</v>
       </c>
       <c r="I50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J50"/>
       <c r="K50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N50" t="s">
         <v>19</v>
       </c>
       <c r="O50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -5719,23 +5719,23 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B51" t="n">
         <v>272489</v>
       </c>
       <c r="C51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D51"/>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F51" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H51" t="n">
         <v>3140</v>
@@ -5747,17 +5747,17 @@
         <v>100267</v>
       </c>
       <c r="K51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M51"/>
       <c r="N51" t="s">
         <v>19</v>
       </c>
       <c r="O51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P51" t="s">
         <v>19</v>
@@ -5768,49 +5768,49 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B52" t="n">
         <v>36798</v>
       </c>
       <c r="C52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F52" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H52" t="n">
         <v>3456</v>
       </c>
       <c r="I52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J52" t="n">
         <v>100355</v>
       </c>
       <c r="K52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N52" t="s">
         <v>19</v>
       </c>
       <c r="O52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P52" t="s">
         <v>19</v>
@@ -5821,45 +5821,45 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B53" t="n">
         <v>44539</v>
       </c>
       <c r="C53" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D53"/>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H53" t="n">
         <v>3659</v>
       </c>
       <c r="I53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J53" t="n">
         <v>100291</v>
       </c>
       <c r="K53" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M53"/>
       <c r="N53" t="s">
         <v>19</v>
       </c>
       <c r="O53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P53" t="s">
         <v>19</v>
@@ -5870,49 +5870,49 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B54" t="n">
         <v>12571</v>
       </c>
       <c r="C54" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G54" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H54" t="n">
         <v>3894</v>
       </c>
       <c r="I54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J54" t="n">
         <v>100291</v>
       </c>
       <c r="K54" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N54" t="s">
         <v>19</v>
       </c>
       <c r="O54" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P54" t="s">
         <v>19</v>
@@ -5923,50 +5923,50 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B55" t="n">
         <v>475844</v>
       </c>
       <c r="C55" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H55" t="n">
         <v>4079</v>
       </c>
       <c r="I55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J55"/>
       <c r="K55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N55" t="s">
         <v>19</v>
       </c>
       <c r="O55" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -5974,50 +5974,50 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B56" t="n">
         <v>475839</v>
       </c>
       <c r="C56" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H56" t="n">
         <v>4080</v>
       </c>
       <c r="I56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J56"/>
       <c r="K56" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L56" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N56" t="s">
         <v>19</v>
       </c>
       <c r="O56" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6025,48 +6025,48 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B57" t="n">
         <v>498838</v>
       </c>
       <c r="C57" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D57"/>
       <c r="E57" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H57" t="n">
         <v>6138</v>
       </c>
       <c r="I57" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J57" t="n">
         <v>100305</v>
       </c>
       <c r="K57" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L57" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M57"/>
       <c r="N57" t="s">
         <v>19</v>
       </c>
       <c r="O57" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P57" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -6074,48 +6074,48 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B58" t="n">
         <v>501520</v>
       </c>
       <c r="C58" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D58"/>
       <c r="E58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G58" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H58" t="n">
         <v>6142</v>
       </c>
       <c r="I58" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J58" t="n">
         <v>100295</v>
       </c>
       <c r="K58" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L58" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M58"/>
       <c r="N58" t="s">
         <v>19</v>
       </c>
       <c r="O58" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -6123,48 +6123,48 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B59" t="n">
         <v>501441</v>
       </c>
       <c r="C59" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D59"/>
       <c r="E59" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G59" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H59" t="n">
         <v>6150</v>
       </c>
       <c r="I59" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J59" t="n">
         <v>100605</v>
       </c>
       <c r="K59" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L59" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M59"/>
       <c r="N59" t="s">
         <v>19</v>
       </c>
       <c r="O59" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -6172,48 +6172,48 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B60" t="n">
         <v>271367</v>
       </c>
       <c r="C60" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D60"/>
       <c r="E60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H60" t="n">
         <v>6153</v>
       </c>
       <c r="I60" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J60" t="n">
         <v>100626</v>
       </c>
       <c r="K60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L60" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M60"/>
       <c r="N60" t="s">
         <v>19</v>
       </c>
       <c r="O60" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -6221,48 +6221,48 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B61" t="n">
         <v>498777</v>
       </c>
       <c r="C61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D61"/>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F61" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H61" t="n">
         <v>6154</v>
       </c>
       <c r="I61" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J61" t="n">
         <v>100628</v>
       </c>
       <c r="K61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L61" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M61"/>
       <c r="N61" t="s">
         <v>19</v>
       </c>
       <c r="O61" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P61" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -6270,48 +6270,48 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B62" t="n">
         <v>227398</v>
       </c>
       <c r="C62" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D62"/>
       <c r="E62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F62" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G62" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H62" t="n">
         <v>6177</v>
       </c>
       <c r="I62" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J62" t="n">
         <v>100625</v>
       </c>
       <c r="K62" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M62"/>
       <c r="N62" t="s">
         <v>19</v>
       </c>
       <c r="O62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P62" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -6319,48 +6319,48 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B63" t="n">
         <v>3770</v>
       </c>
       <c r="C63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D63"/>
       <c r="E63" t="s">
         <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G63" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H63" t="n">
         <v>10004</v>
       </c>
       <c r="I63" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J63" t="n">
         <v>100688</v>
       </c>
       <c r="K63" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L63" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M63"/>
       <c r="N63" t="s">
         <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P63" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -6368,23 +6368,23 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B64" t="n">
         <v>501500</v>
       </c>
       <c r="C64" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D64"/>
       <c r="E64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G64" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H64" t="n">
         <v>20116</v>
@@ -6396,17 +6396,17 @@
         <v>90</v>
       </c>
       <c r="K64" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L64" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M64"/>
       <c r="N64" t="s">
         <v>19</v>
       </c>
       <c r="O64" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P64" t="s">
         <v>19</v>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B65" t="n">
         <v>501494</v>
@@ -6425,13 +6425,13 @@
       <c r="C65"/>
       <c r="D65"/>
       <c r="E65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F65" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G65" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H65" t="n">
         <v>20117</v>
@@ -6443,17 +6443,17 @@
         <v>90</v>
       </c>
       <c r="K65" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L65" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M65"/>
       <c r="N65" t="s">
         <v>19</v>
       </c>
       <c r="O65" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P65" t="s">
         <v>19</v>
@@ -6464,23 +6464,23 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B66" t="n">
         <v>122938</v>
       </c>
       <c r="C66" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D66"/>
       <c r="E66" t="s">
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G66" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H66" t="n">
         <v>20126</v>
@@ -6492,17 +6492,17 @@
         <v>100695</v>
       </c>
       <c r="K66" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L66" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M66"/>
       <c r="N66" t="s">
         <v>19</v>
       </c>
       <c r="O66" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P66" t="s">
         <v>19</v>
@@ -6513,43 +6513,43 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B67" t="n">
         <v>401465</v>
       </c>
       <c r="C67" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D67"/>
       <c r="E67" t="s">
         <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G67" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H67" t="n">
         <v>20127</v>
       </c>
       <c r="I67" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J67"/>
       <c r="K67" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L67" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M67"/>
       <c r="N67" t="s">
         <v>19</v>
       </c>
       <c r="O67" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P67" t="s">
         <v>19</v>
@@ -6560,47 +6560,47 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B68" t="n">
         <v>153151</v>
       </c>
       <c r="C68" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E68" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G68" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H68" t="n">
         <v>20161</v>
       </c>
       <c r="I68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J68"/>
       <c r="K68" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N68" t="s">
         <v>19</v>
       </c>
       <c r="O68" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P68" t="s">
         <v>19</v>
@@ -6611,23 +6611,23 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B69" t="n">
         <v>501479</v>
       </c>
       <c r="C69" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D69"/>
       <c r="E69" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F69" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G69" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H69" t="n">
         <v>21000</v>
@@ -6639,17 +6639,17 @@
         <v>1001</v>
       </c>
       <c r="K69" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M69"/>
       <c r="N69" t="s">
         <v>19</v>
       </c>
       <c r="O69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P69" t="s">
         <v>19</v>
@@ -6660,47 +6660,47 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B70" t="n">
         <v>499393</v>
       </c>
       <c r="C70" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D70" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G70" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H70" t="n">
         <v>21001</v>
       </c>
       <c r="I70" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J70"/>
       <c r="K70" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L70" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M70" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N70" t="s">
         <v>19</v>
       </c>
       <c r="O70" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P70" t="s">
         <v>19</v>
@@ -6711,43 +6711,43 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B71" t="n">
         <v>218468</v>
       </c>
       <c r="C71" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D71"/>
       <c r="E71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F71" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G71" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H71" t="n">
         <v>21021</v>
       </c>
       <c r="I71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J71"/>
       <c r="K71" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L71" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M71"/>
       <c r="N71" t="s">
         <v>19</v>
       </c>
       <c r="O71" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P71" t="s">
         <v>19</v>
@@ -6758,16 +6758,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B72" t="n">
         <v>502366</v>
       </c>
       <c r="C72" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
@@ -6776,29 +6776,29 @@
         <v>20</v>
       </c>
       <c r="G72" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H72" t="n">
         <v>21022</v>
       </c>
       <c r="I72" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J72"/>
       <c r="K72" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L72" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N72" t="s">
         <v>19</v>
       </c>
       <c r="O72" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P72" t="s">
         <v>19</v>
@@ -6809,50 +6809,50 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B73" t="n">
         <v>394466</v>
       </c>
       <c r="C73" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D73" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G73" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H73" t="n">
         <v>22037</v>
       </c>
       <c r="I73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J73"/>
       <c r="K73" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L73" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M73" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N73" t="s">
         <v>19</v>
       </c>
       <c r="O73" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P73" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -6860,50 +6860,50 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B74" t="n">
         <v>394466</v>
       </c>
       <c r="C74" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D74" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G74" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H74" t="n">
         <v>22038</v>
       </c>
       <c r="I74" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J74"/>
       <c r="K74" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L74" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M74" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N74" t="s">
         <v>19</v>
       </c>
       <c r="O74" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P74" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -6911,50 +6911,50 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B75" t="n">
         <v>394466</v>
       </c>
       <c r="C75" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D75" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G75" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H75" t="n">
         <v>22039</v>
       </c>
       <c r="I75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J75"/>
       <c r="K75" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L75" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M75" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N75" t="s">
         <v>19</v>
       </c>
       <c r="O75" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P75" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6962,50 +6962,50 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B76" t="n">
         <v>394466</v>
       </c>
       <c r="C76" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D76" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G76" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H76" t="n">
         <v>22040</v>
       </c>
       <c r="I76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J76"/>
       <c r="K76" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L76" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M76" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N76" t="s">
         <v>19</v>
       </c>
       <c r="O76" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P76" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -7013,43 +7013,43 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B77" t="n">
         <v>1768</v>
       </c>
       <c r="C77" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D77"/>
       <c r="E77" t="s">
         <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G77" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H77" t="n">
         <v>22150</v>
       </c>
       <c r="I77" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J77"/>
       <c r="K77" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L77" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M77"/>
       <c r="N77" t="s">
         <v>19</v>
       </c>
       <c r="O77" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P77" t="s">
         <v>19</v>
@@ -7060,43 +7060,43 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B78" t="n">
         <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D78"/>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G78" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H78" t="n">
         <v>22155</v>
       </c>
       <c r="I78" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J78"/>
       <c r="K78" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L78" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M78"/>
       <c r="N78" t="s">
         <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P78" t="s">
         <v>19</v>
@@ -7107,50 +7107,50 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B79" t="n">
         <v>39695</v>
       </c>
       <c r="C79" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D79" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E79" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F79" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G79" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H79" t="n">
         <v>22426</v>
       </c>
       <c r="I79" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J79"/>
       <c r="K79" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L79" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M79" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N79" t="s">
         <v>19</v>
       </c>
       <c r="O79" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P79" t="s">
-        <v>414</v>
+        <v>29</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -7170,7 +7170,7 @@
         <v>417</v>
       </c>
       <c r="E80" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F80" t="s">
         <v>418</v>
@@ -7182,7 +7182,7 @@
         <v>23099</v>
       </c>
       <c r="I80" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J80"/>
       <c r="K80" t="s">
@@ -7201,7 +7201,7 @@
         <v>421</v>
       </c>
       <c r="P80" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -7233,7 +7233,7 @@
         <v>24003</v>
       </c>
       <c r="I81" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J81"/>
       <c r="K81" t="s">
@@ -7284,7 +7284,7 @@
         <v>24005</v>
       </c>
       <c r="I82" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J82"/>
       <c r="K82" t="s">
@@ -7335,7 +7335,7 @@
         <v>24006</v>
       </c>
       <c r="I83" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J83"/>
       <c r="K83" t="s">
@@ -7354,7 +7354,7 @@
         <v>438</v>
       </c>
       <c r="P83" t="s">
-        <v>414</v>
+        <v>29</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7386,7 +7386,7 @@
         <v>24024</v>
       </c>
       <c r="I84" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J84"/>
       <c r="K84" t="s">
@@ -7405,7 +7405,7 @@
         <v>446</v>
       </c>
       <c r="P84" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
         <v>417</v>
       </c>
       <c r="E85" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F85" t="s">
         <v>449</v>
@@ -7437,7 +7437,7 @@
         <v>24503</v>
       </c>
       <c r="I85" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J85"/>
       <c r="K85" t="s">
@@ -7476,7 +7476,7 @@
         <v>417</v>
       </c>
       <c r="E86" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F86" t="s">
         <v>449</v>
@@ -7488,7 +7488,7 @@
         <v>24504</v>
       </c>
       <c r="I86" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J86"/>
       <c r="K86" t="s">
@@ -7527,7 +7527,7 @@
         <v>417</v>
       </c>
       <c r="E87" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F87" t="s">
         <v>449</v>
@@ -7539,7 +7539,7 @@
         <v>24505</v>
       </c>
       <c r="I87" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J87"/>
       <c r="K87" t="s">
@@ -7578,7 +7578,7 @@
         <v>417</v>
       </c>
       <c r="E88" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F88" t="s">
         <v>449</v>
@@ -7590,7 +7590,7 @@
         <v>24507</v>
       </c>
       <c r="I88" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J88"/>
       <c r="K88" t="s">
@@ -7629,7 +7629,7 @@
         <v>470</v>
       </c>
       <c r="E89" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F89" t="s">
         <v>449</v>
@@ -7641,7 +7641,7 @@
         <v>24508</v>
       </c>
       <c r="I89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J89"/>
       <c r="K89" t="s">
@@ -7680,7 +7680,7 @@
         <v>477</v>
       </c>
       <c r="E90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F90" t="s">
         <v>478</v>
@@ -7692,7 +7692,7 @@
         <v>30010</v>
       </c>
       <c r="I90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J90"/>
       <c r="K90" t="s">
@@ -7731,7 +7731,7 @@
         <v>485</v>
       </c>
       <c r="E91" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F91" t="s">
         <v>478</v>
@@ -7743,7 +7743,7 @@
         <v>30020</v>
       </c>
       <c r="I91" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J91"/>
       <c r="K91" t="s">
@@ -7782,7 +7782,7 @@
         <v>417</v>
       </c>
       <c r="E92" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F92" t="s">
         <v>478</v>
@@ -7794,7 +7794,7 @@
         <v>30030</v>
       </c>
       <c r="I92" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J92"/>
       <c r="K92" t="s">
@@ -7833,7 +7833,7 @@
         <v>496</v>
       </c>
       <c r="E93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F93" t="s">
         <v>478</v>
@@ -7845,7 +7845,7 @@
         <v>30040</v>
       </c>
       <c r="I93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J93"/>
       <c r="K93" t="s">
@@ -7884,7 +7884,7 @@
         <v>502</v>
       </c>
       <c r="E94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F94" t="s">
         <v>478</v>
@@ -7896,7 +7896,7 @@
         <v>30050</v>
       </c>
       <c r="I94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J94"/>
       <c r="K94" t="s">
@@ -7935,7 +7935,7 @@
         <v>485</v>
       </c>
       <c r="E95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F95" t="s">
         <v>478</v>
@@ -7947,7 +7947,7 @@
         <v>30060</v>
       </c>
       <c r="I95" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J95"/>
       <c r="K95" t="s">
@@ -7986,7 +7986,7 @@
         <v>417</v>
       </c>
       <c r="E96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F96" t="s">
         <v>478</v>
@@ -7998,7 +7998,7 @@
         <v>30070</v>
       </c>
       <c r="I96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J96"/>
       <c r="K96" t="s">
@@ -8037,7 +8037,7 @@
         <v>518</v>
       </c>
       <c r="E97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F97" t="s">
         <v>478</v>
@@ -8049,7 +8049,7 @@
         <v>30080</v>
       </c>
       <c r="I97" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J97"/>
       <c r="K97" t="s">
@@ -8088,7 +8088,7 @@
         <v>417</v>
       </c>
       <c r="E98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F98" t="s">
         <v>478</v>
@@ -8100,7 +8100,7 @@
         <v>30090</v>
       </c>
       <c r="I98" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J98"/>
       <c r="K98" t="s">
@@ -8139,7 +8139,7 @@
         <v>496</v>
       </c>
       <c r="E99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F99" t="s">
         <v>478</v>
@@ -8151,7 +8151,7 @@
         <v>30100</v>
       </c>
       <c r="I99" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J99"/>
       <c r="K99" t="s">
@@ -8190,7 +8190,7 @@
         <v>417</v>
       </c>
       <c r="E100" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F100" t="s">
         <v>478</v>
@@ -8202,7 +8202,7 @@
         <v>30110</v>
       </c>
       <c r="I100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J100"/>
       <c r="K100" t="s">
@@ -8241,7 +8241,7 @@
         <v>518</v>
       </c>
       <c r="E101" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F101" t="s">
         <v>478</v>
@@ -8253,7 +8253,7 @@
         <v>30120</v>
       </c>
       <c r="I101" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J101"/>
       <c r="K101" t="s">
@@ -8292,7 +8292,7 @@
         <v>518</v>
       </c>
       <c r="E102" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F102" t="s">
         <v>478</v>
@@ -8304,7 +8304,7 @@
         <v>30130</v>
       </c>
       <c r="I102" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J102"/>
       <c r="K102" t="s">
@@ -8343,7 +8343,7 @@
         <v>518</v>
       </c>
       <c r="E103" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F103" t="s">
         <v>478</v>
@@ -8355,7 +8355,7 @@
         <v>30140</v>
       </c>
       <c r="I103" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J103"/>
       <c r="K103" t="s">
@@ -8394,7 +8394,7 @@
         <v>518</v>
       </c>
       <c r="E104" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F104" t="s">
         <v>478</v>
@@ -8406,7 +8406,7 @@
         <v>30150</v>
       </c>
       <c r="I104" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J104"/>
       <c r="K104" t="s">
@@ -8445,7 +8445,7 @@
         <v>518</v>
       </c>
       <c r="E105" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F105" t="s">
         <v>478</v>
@@ -8457,7 +8457,7 @@
         <v>30160</v>
       </c>
       <c r="I105" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J105"/>
       <c r="K105" t="s">
@@ -8496,7 +8496,7 @@
         <v>518</v>
       </c>
       <c r="E106" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F106" t="s">
         <v>478</v>
@@ -8508,7 +8508,7 @@
         <v>30170</v>
       </c>
       <c r="I106" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J106"/>
       <c r="K106" t="s">
@@ -8547,7 +8547,7 @@
         <v>417</v>
       </c>
       <c r="E107" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F107" t="s">
         <v>478</v>
@@ -8559,7 +8559,7 @@
         <v>30180</v>
       </c>
       <c r="I107" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J107"/>
       <c r="K107" t="s">
@@ -8598,7 +8598,7 @@
         <v>417</v>
       </c>
       <c r="E108" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F108" t="s">
         <v>478</v>
@@ -8610,7 +8610,7 @@
         <v>30190</v>
       </c>
       <c r="I108" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J108"/>
       <c r="K108" t="s">
@@ -8649,7 +8649,7 @@
         <v>417</v>
       </c>
       <c r="E109" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F109" t="s">
         <v>478</v>
@@ -8661,7 +8661,7 @@
         <v>30200</v>
       </c>
       <c r="I109" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J109"/>
       <c r="K109" t="s">
@@ -8700,7 +8700,7 @@
         <v>417</v>
       </c>
       <c r="E110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F110" t="s">
         <v>478</v>
@@ -8712,7 +8712,7 @@
         <v>30210</v>
       </c>
       <c r="I110" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J110"/>
       <c r="K110" t="s">
@@ -8751,7 +8751,7 @@
         <v>417</v>
       </c>
       <c r="E111" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F111" t="s">
         <v>478</v>
@@ -8763,7 +8763,7 @@
         <v>30220</v>
       </c>
       <c r="I111" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J111"/>
       <c r="K111" t="s">
@@ -8802,7 +8802,7 @@
         <v>417</v>
       </c>
       <c r="E112" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F112" t="s">
         <v>478</v>
@@ -8814,7 +8814,7 @@
         <v>30230</v>
       </c>
       <c r="I112" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J112"/>
       <c r="K112" t="s">
@@ -8853,7 +8853,7 @@
         <v>417</v>
       </c>
       <c r="E113" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F113" t="s">
         <v>478</v>
@@ -8865,7 +8865,7 @@
         <v>30240</v>
       </c>
       <c r="I113" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J113"/>
       <c r="K113" t="s">
@@ -8904,7 +8904,7 @@
         <v>477</v>
       </c>
       <c r="E114" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F114" t="s">
         <v>478</v>
@@ -8916,7 +8916,7 @@
         <v>30250</v>
       </c>
       <c r="I114" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J114"/>
       <c r="K114" t="s">
@@ -8955,7 +8955,7 @@
         <v>496</v>
       </c>
       <c r="E115" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F115" t="s">
         <v>478</v>
@@ -8967,7 +8967,7 @@
         <v>30260</v>
       </c>
       <c r="I115" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J115"/>
       <c r="K115" t="s">
@@ -9006,7 +9006,7 @@
         <v>496</v>
       </c>
       <c r="E116" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F116" t="s">
         <v>478</v>
@@ -9018,7 +9018,7 @@
         <v>30270</v>
       </c>
       <c r="I116" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J116"/>
       <c r="K116" t="s">
@@ -9057,7 +9057,7 @@
         <v>620</v>
       </c>
       <c r="E117" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F117" t="s">
         <v>478</v>
@@ -9069,7 +9069,7 @@
         <v>30280</v>
       </c>
       <c r="I117" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J117"/>
       <c r="K117" t="s">
@@ -9108,7 +9108,7 @@
         <v>417</v>
       </c>
       <c r="E118" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F118" t="s">
         <v>478</v>
@@ -9120,7 +9120,7 @@
         <v>30290</v>
       </c>
       <c r="I118" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J118"/>
       <c r="K118" t="s">
@@ -9159,7 +9159,7 @@
         <v>477</v>
       </c>
       <c r="E119" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F119" t="s">
         <v>478</v>
@@ -9171,7 +9171,7 @@
         <v>30300</v>
       </c>
       <c r="I119" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J119"/>
       <c r="K119" t="s">
@@ -9210,7 +9210,7 @@
         <v>636</v>
       </c>
       <c r="E120" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F120" t="s">
         <v>637</v>
@@ -9222,7 +9222,7 @@
         <v>30500</v>
       </c>
       <c r="I120" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J120"/>
       <c r="K120" t="s">
@@ -9261,7 +9261,7 @@
         <v>644</v>
       </c>
       <c r="E121" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F121" t="s">
         <v>645</v>
@@ -9273,7 +9273,7 @@
         <v>30600</v>
       </c>
       <c r="I121" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J121"/>
       <c r="K121" t="s">
@@ -9312,7 +9312,7 @@
         <v>652</v>
       </c>
       <c r="E122" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F122" t="s">
         <v>645</v>
@@ -9324,7 +9324,7 @@
         <v>30610</v>
       </c>
       <c r="I122" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J122"/>
       <c r="K122" t="s">
@@ -9363,7 +9363,7 @@
         <v>652</v>
       </c>
       <c r="E123" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F123" t="s">
         <v>645</v>
@@ -9375,7 +9375,7 @@
         <v>30620</v>
       </c>
       <c r="I123" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J123"/>
       <c r="K123" t="s">
@@ -9414,7 +9414,7 @@
         <v>644</v>
       </c>
       <c r="E124" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F124" t="s">
         <v>645</v>
@@ -9426,7 +9426,7 @@
         <v>30630</v>
       </c>
       <c r="I124" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J124"/>
       <c r="K124" t="s">
@@ -9465,7 +9465,7 @@
         <v>644</v>
       </c>
       <c r="E125" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F125" t="s">
         <v>645</v>
@@ -9477,7 +9477,7 @@
         <v>30640</v>
       </c>
       <c r="I125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J125"/>
       <c r="K125" t="s">
@@ -9516,7 +9516,7 @@
         <v>652</v>
       </c>
       <c r="E126" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F126" t="s">
         <v>645</v>
@@ -9528,7 +9528,7 @@
         <v>30650</v>
       </c>
       <c r="I126" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J126"/>
       <c r="K126" t="s">
@@ -9567,7 +9567,7 @@
         <v>677</v>
       </c>
       <c r="E127" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F127" t="s">
         <v>645</v>
@@ -9579,7 +9579,7 @@
         <v>30660</v>
       </c>
       <c r="I127" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J127"/>
       <c r="K127" t="s">
@@ -9618,7 +9618,7 @@
         <v>684</v>
       </c>
       <c r="E128" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F128" t="s">
         <v>645</v>
@@ -9630,7 +9630,7 @@
         <v>30670</v>
       </c>
       <c r="I128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J128"/>
       <c r="K128" t="s">
@@ -9669,7 +9669,7 @@
         <v>684</v>
       </c>
       <c r="E129" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F129" t="s">
         <v>645</v>
@@ -9681,7 +9681,7 @@
         <v>30680</v>
       </c>
       <c r="I129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J129"/>
       <c r="K129" t="s">
@@ -9720,7 +9720,7 @@
         <v>684</v>
       </c>
       <c r="E130" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F130" t="s">
         <v>645</v>
@@ -9732,7 +9732,7 @@
         <v>30690</v>
       </c>
       <c r="I130" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J130"/>
       <c r="K130" t="s">
@@ -9771,7 +9771,7 @@
         <v>677</v>
       </c>
       <c r="E131" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F131" t="s">
         <v>645</v>
@@ -9783,7 +9783,7 @@
         <v>30700</v>
       </c>
       <c r="I131" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J131"/>
       <c r="K131" t="s">
@@ -9822,7 +9822,7 @@
         <v>636</v>
       </c>
       <c r="E132" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F132" t="s">
         <v>645</v>
@@ -9834,7 +9834,7 @@
         <v>30710</v>
       </c>
       <c r="I132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J132"/>
       <c r="K132" t="s">
@@ -9873,7 +9873,7 @@
         <v>636</v>
       </c>
       <c r="E133" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F133" t="s">
         <v>645</v>
@@ -9885,7 +9885,7 @@
         <v>30720</v>
       </c>
       <c r="I133" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J133"/>
       <c r="K133" t="s">
@@ -9924,7 +9924,7 @@
         <v>652</v>
       </c>
       <c r="E134" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F134" t="s">
         <v>645</v>
@@ -9936,7 +9936,7 @@
         <v>30730</v>
       </c>
       <c r="I134" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J134"/>
       <c r="K134" t="s">
@@ -9975,7 +9975,7 @@
         <v>684</v>
       </c>
       <c r="E135" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F135" t="s">
         <v>645</v>
@@ -9987,7 +9987,7 @@
         <v>30740</v>
       </c>
       <c r="I135" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J135"/>
       <c r="K135" t="s">
@@ -10026,7 +10026,7 @@
         <v>725</v>
       </c>
       <c r="E136" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F136" t="s">
         <v>645</v>
@@ -10038,7 +10038,7 @@
         <v>30750</v>
       </c>
       <c r="I136" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J136"/>
       <c r="K136" t="s">
@@ -10077,7 +10077,7 @@
         <v>684</v>
       </c>
       <c r="E137" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F137" t="s">
         <v>645</v>
@@ -10089,7 +10089,7 @@
         <v>30760</v>
       </c>
       <c r="I137" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J137"/>
       <c r="K137" t="s">
@@ -10128,7 +10128,7 @@
         <v>736</v>
       </c>
       <c r="E138" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F138" t="s">
         <v>645</v>
@@ -10140,7 +10140,7 @@
         <v>30770</v>
       </c>
       <c r="I138" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J138"/>
       <c r="K138" t="s">
@@ -10179,7 +10179,7 @@
         <v>684</v>
       </c>
       <c r="E139" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F139" t="s">
         <v>645</v>
@@ -10191,7 +10191,7 @@
         <v>30780</v>
       </c>
       <c r="I139" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J139"/>
       <c r="K139" t="s">
@@ -10230,7 +10230,7 @@
         <v>736</v>
       </c>
       <c r="E140" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F140" t="s">
         <v>645</v>
@@ -10242,7 +10242,7 @@
         <v>30790</v>
       </c>
       <c r="I140" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J140"/>
       <c r="K140" t="s">
@@ -10281,7 +10281,7 @@
         <v>753</v>
       </c>
       <c r="E141" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F141" t="s">
         <v>645</v>
@@ -10293,7 +10293,7 @@
         <v>30800</v>
       </c>
       <c r="I141" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J141"/>
       <c r="K141" t="s">
@@ -10332,7 +10332,7 @@
         <v>684</v>
       </c>
       <c r="E142" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F142" t="s">
         <v>645</v>
@@ -10344,7 +10344,7 @@
         <v>30810</v>
       </c>
       <c r="I142" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J142"/>
       <c r="K142" t="s">
@@ -10383,7 +10383,7 @@
         <v>764</v>
       </c>
       <c r="E143" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F143" t="s">
         <v>645</v>
@@ -10395,7 +10395,7 @@
         <v>30820</v>
       </c>
       <c r="I143" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J143"/>
       <c r="K143" t="s">
@@ -10434,7 +10434,7 @@
         <v>736</v>
       </c>
       <c r="E144" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F144" t="s">
         <v>645</v>
@@ -10446,7 +10446,7 @@
         <v>30830</v>
       </c>
       <c r="I144" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J144"/>
       <c r="K144" t="s">
@@ -10485,7 +10485,7 @@
         <v>677</v>
       </c>
       <c r="E145" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F145" t="s">
         <v>645</v>
@@ -10497,7 +10497,7 @@
         <v>30840</v>
       </c>
       <c r="I145" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J145"/>
       <c r="K145" t="s">
@@ -10536,7 +10536,7 @@
         <v>736</v>
       </c>
       <c r="E146" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F146" t="s">
         <v>645</v>
@@ -10548,7 +10548,7 @@
         <v>30850</v>
       </c>
       <c r="I146" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J146"/>
       <c r="K146" t="s">
@@ -10587,7 +10587,7 @@
         <v>684</v>
       </c>
       <c r="E147" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F147" t="s">
         <v>645</v>
@@ -10599,7 +10599,7 @@
         <v>30870</v>
       </c>
       <c r="I147" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J147"/>
       <c r="K147" t="s">
@@ -10638,7 +10638,7 @@
         <v>677</v>
       </c>
       <c r="E148" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F148" t="s">
         <v>645</v>
@@ -10650,7 +10650,7 @@
         <v>30880</v>
       </c>
       <c r="I148" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J148"/>
       <c r="K148" t="s">
@@ -10689,7 +10689,7 @@
         <v>736</v>
       </c>
       <c r="E149" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F149" t="s">
         <v>645</v>
@@ -10701,7 +10701,7 @@
         <v>30890</v>
       </c>
       <c r="I149" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J149"/>
       <c r="K149" t="s">
@@ -10767,7 +10767,7 @@
         <v>798</v>
       </c>
       <c r="P150" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
@@ -10844,7 +10844,7 @@
         <v>40011</v>
       </c>
       <c r="I152" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J152"/>
       <c r="K152" t="s">
@@ -10881,7 +10881,7 @@
         <v>815</v>
       </c>
       <c r="E153" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F153" t="s">
         <v>816</v>
@@ -10893,7 +10893,7 @@
         <v>100006</v>
       </c>
       <c r="I153" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J153"/>
       <c r="K153" t="s">
@@ -10932,7 +10932,7 @@
         <v>815</v>
       </c>
       <c r="E154" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F154" t="s">
         <v>816</v>
@@ -10944,7 +10944,7 @@
         <v>100007</v>
       </c>
       <c r="I154" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J154"/>
       <c r="K154" t="s">
@@ -10983,7 +10983,7 @@
         <v>827</v>
       </c>
       <c r="E155" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F155" t="s">
         <v>816</v>
@@ -10995,7 +10995,7 @@
         <v>100012</v>
       </c>
       <c r="I155" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J155"/>
       <c r="K155" t="s">
@@ -11034,7 +11034,7 @@
         <v>833</v>
       </c>
       <c r="E156" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F156" t="s">
         <v>816</v>
@@ -11046,7 +11046,7 @@
         <v>100013</v>
       </c>
       <c r="I156" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J156"/>
       <c r="K156" t="s">
@@ -11114,7 +11114,7 @@
         <v>837</v>
       </c>
       <c r="P157" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>842</v>
       </c>
       <c r="P158" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
@@ -11212,7 +11212,7 @@
         <v>847</v>
       </c>
       <c r="P159" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
@@ -11261,7 +11261,7 @@
         <v>851</v>
       </c>
       <c r="P160" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>856</v>
       </c>
       <c r="P161" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
@@ -11359,7 +11359,7 @@
         <v>860</v>
       </c>
       <c r="P162" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q162" t="n">
         <v>0</v>
@@ -11408,7 +11408,7 @@
         <v>864</v>
       </c>
       <c r="P163" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q163" t="n">
         <v>0</v>
@@ -11457,7 +11457,7 @@
         <v>868</v>
       </c>
       <c r="P164" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q164" t="n">
         <v>0</v>
@@ -11506,7 +11506,7 @@
         <v>872</v>
       </c>
       <c r="P165" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q165" t="n">
         <v>0</v>
@@ -11555,7 +11555,7 @@
         <v>877</v>
       </c>
       <c r="P166" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
@@ -11604,7 +11604,7 @@
         <v>881</v>
       </c>
       <c r="P167" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q167" t="n">
         <v>0</v>
@@ -11653,7 +11653,7 @@
         <v>885</v>
       </c>
       <c r="P168" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q168" t="n">
         <v>0</v>
@@ -11702,7 +11702,7 @@
         <v>889</v>
       </c>
       <c r="P169" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q169" t="n">
         <v>0</v>
@@ -11751,7 +11751,7 @@
         <v>893</v>
       </c>
       <c r="P170" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q170" t="n">
         <v>0</v>
@@ -11800,7 +11800,7 @@
         <v>897</v>
       </c>
       <c r="P171" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q171" t="n">
         <v>0</v>
@@ -11849,7 +11849,7 @@
         <v>902</v>
       </c>
       <c r="P172" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q172" t="n">
         <v>0</v>
@@ -11898,7 +11898,7 @@
         <v>906</v>
       </c>
       <c r="P173" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q173" t="n">
         <v>0</v>
@@ -11947,7 +11947,7 @@
         <v>910</v>
       </c>
       <c r="P174" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q174" t="n">
         <v>0</v>
@@ -11996,7 +11996,7 @@
         <v>915</v>
       </c>
       <c r="P175" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q175" t="n">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         <v>920</v>
       </c>
       <c r="P176" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q176" t="n">
         <v>0</v>
@@ -12094,7 +12094,7 @@
         <v>924</v>
       </c>
       <c r="P177" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q177" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>928</v>
       </c>
       <c r="P178" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q178" t="n">
         <v>0</v>
@@ -12192,7 +12192,7 @@
         <v>932</v>
       </c>
       <c r="P179" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q179" t="n">
         <v>0</v>
@@ -12241,7 +12241,7 @@
         <v>937</v>
       </c>
       <c r="P180" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q180" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
         <v>941</v>
       </c>
       <c r="P181" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q181" t="n">
         <v>0</v>
@@ -12339,7 +12339,7 @@
         <v>946</v>
       </c>
       <c r="P182" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q182" t="n">
         <v>0</v>
